--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>83106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R6" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>83106</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R7" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B6" t="n">
-        <v>83106</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R6" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>83106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R7" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>83107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R6" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>83106</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R7" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B6" t="n">
-        <v>83110</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R6" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>83110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R7" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>83110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R6" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>83110</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R7" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B6" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R6" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R7" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R6" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R7" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B6" t="n">
-        <v>83120</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R6" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>83122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R7" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58808-2021 artfynd.xlsx
+++ b/artfynd/A 58808-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131689518</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131689076</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131689410</v>
       </c>
       <c r="B4" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131689467</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131689449</v>
+        <v>131689357</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>83163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769738</v>
+        <v>769698</v>
       </c>
       <c r="R6" t="n">
-        <v>7159345</v>
+        <v>7159280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131689357</v>
+        <v>131689449</v>
       </c>
       <c r="B7" t="n">
-        <v>83161</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769698</v>
+        <v>769738</v>
       </c>
       <c r="R7" t="n">
-        <v>7159280</v>
+        <v>7159345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
